--- a/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>AHG</t>
   </si>
@@ -656,128 +656,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44104</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43921</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43738</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>1400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5400</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>5</v>
       </c>
@@ -799,23 +806,26 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>5</v>
       </c>
@@ -837,8 +847,11 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -853,46 +866,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>-200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>200</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
       </c>
       <c r="I12" s="3">
+        <v>200</v>
+      </c>
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -929,8 +946,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,35 +960,38 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>29200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1005,8 +1028,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,84 +1044,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E17" s="3">
         <v>14500</v>
       </c>
-      <c r="E17" s="3">
-        <v>12900</v>
-      </c>
       <c r="F17" s="3">
+        <v>12100</v>
+      </c>
+      <c r="G17" s="3">
         <v>500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>49300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13200</v>
       </c>
-      <c r="E18" s="3">
-        <v>-1000</v>
-      </c>
       <c r="F18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G18" s="3">
         <v>5300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-47500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1110,8 +1143,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1119,48 +1153,51 @@
         <v>-700</v>
       </c>
       <c r="E20" s="3">
-        <v>1900</v>
+        <v>-700</v>
       </c>
       <c r="F20" s="3">
-        <v>-400</v>
+        <v>1800</v>
       </c>
       <c r="G20" s="3">
         <v>-400</v>
       </c>
       <c r="H20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3">
-        <v>900</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1700</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>5</v>
@@ -1186,8 +1223,11 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1224,46 +1264,52 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13900</v>
       </c>
-      <c r="E23" s="3">
-        <v>800</v>
-      </c>
       <c r="F23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G23" s="3">
         <v>4900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-47500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1274,34 +1320,37 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1338,84 +1387,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13900</v>
       </c>
-      <c r="E26" s="3">
-        <v>800</v>
-      </c>
       <c r="F26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G26" s="3">
         <v>4800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-46900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14000</v>
       </c>
-      <c r="E27" s="3">
-        <v>800</v>
-      </c>
       <c r="F27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G27" s="3">
         <v>4800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-46900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1452,46 +1510,52 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E29" s="3">
         <v>11800</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F29" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G29" s="3">
         <v>-12700</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-30500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-6100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-6800</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" s="3">
         <v>13100</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1528,8 +1592,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1566,8 +1633,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1575,75 +1645,81 @@
         <v>700</v>
       </c>
       <c r="E32" s="3">
-        <v>-1900</v>
+        <v>700</v>
       </c>
       <c r="F32" s="3">
-        <v>400</v>
+        <v>-1800</v>
       </c>
       <c r="G32" s="3">
         <v>400</v>
       </c>
       <c r="H32" s="3">
+        <v>400</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-53600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1680,89 +1756,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-53600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44104</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43921</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43738</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1777,8 +1862,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1793,46 +1879,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E41" s="3">
         <v>7900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>57400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1869,61 +1959,67 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E43" s="3">
         <v>9200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>36200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>37000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7800</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
@@ -1939,90 +2035,99 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E46" s="3">
         <v>20500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>62800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>30100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>47900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>52000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>58500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>97700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>95300</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2032,46 +2137,49 @@
       <c r="E47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
       </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>23900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>57800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>81300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>70600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
-        <v>0</v>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <v>100</v>
@@ -2083,22 +2191,25 @@
         <v>100</v>
       </c>
       <c r="J48" s="3">
+        <v>100</v>
+      </c>
+      <c r="K48" s="3">
         <v>800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1300</v>
       </c>
       <c r="N48" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2135,8 +2246,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2173,8 +2287,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2211,8 +2328,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2225,32 +2345,35 @@
       <c r="F52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3">
         <v>10100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>3800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>33700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2287,46 +2410,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E54" s="3">
         <v>20500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>60200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>80500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>133300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>146800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>173300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2341,8 +2470,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2357,8 +2487,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2395,122 +2526,134 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="E58" s="3">
         <v>9700</v>
       </c>
       <c r="F58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="G58" s="3">
         <v>37200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E60" s="3">
         <v>11600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>50500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2530,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>20000</v>
@@ -2545,10 +2688,13 @@
         <v>20000</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+        <v>20000</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2564,29 +2710,32 @@
       <c r="G62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2623,8 +2772,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2661,8 +2813,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2699,8 +2854,11 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2708,37 +2866,40 @@
         <v>11700</v>
       </c>
       <c r="E66" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F66" s="3">
         <v>11000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2753,8 +2914,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2791,8 +2953,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2829,8 +2994,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2867,8 +3035,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2905,46 +3076,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-54500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-52300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-53100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-45200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-36300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-25000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>52200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>62600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>69800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>62300</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2981,8 +3158,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3019,8 +3199,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3057,46 +3240,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E76" s="3">
         <v>8700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>100400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>114600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>120500</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3133,89 +3322,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44104</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43921</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43738</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-53600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3230,19 +3428,20 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
@@ -3256,8 +3455,8 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3268,8 +3467,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3306,8 +3508,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3344,8 +3549,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3382,8 +3590,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3420,8 +3631,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3458,20 +3672,23 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>5</v>
       </c>
@@ -3484,8 +3701,8 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -3496,8 +3713,11 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3512,8 +3732,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3550,8 +3771,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3588,8 +3812,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3626,20 +3853,23 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>20000</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3652,8 +3882,8 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -3664,8 +3894,11 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3680,8 +3913,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3718,8 +3952,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3756,8 +3993,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3794,8 +4034,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3832,20 +4075,23 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-27500</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>5</v>
       </c>
@@ -3858,8 +4104,8 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -3870,20 +4116,23 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>2700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>5</v>
       </c>
@@ -3896,8 +4145,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3908,20 +4157,23 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11900</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G102" s="3" t="s">
         <v>5</v>
       </c>
@@ -3934,8 +4186,8 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -3944,6 +4196,9 @@
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>AHG</t>
   </si>
@@ -656,138 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43921</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43555</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>1400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5400</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>5</v>
       </c>
@@ -809,26 +816,29 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>400</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>5</v>
       </c>
@@ -850,8 +860,11 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -867,8 +880,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -878,38 +892,41 @@
       <c r="E12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>-200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>200</v>
       </c>
       <c r="I12" s="3">
         <v>200</v>
       </c>
       <c r="J12" s="3">
+        <v>200</v>
+      </c>
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1900</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -949,8 +966,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -963,35 +983,38 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>29200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1031,8 +1054,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,90 +1071,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E17" s="3">
         <v>3200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>49300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-47500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1144,64 +1177,68 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-700</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>-700</v>
       </c>
       <c r="F20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G20" s="3">
         <v>1800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-400</v>
       </c>
       <c r="H20" s="3">
         <v>-400</v>
       </c>
       <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3">
         <v>1700</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1226,8 +1263,11 @@
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1267,49 +1307,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-47500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1323,34 +1369,37 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1390,90 +1439,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-46900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-46900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1513,49 +1571,55 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>11800</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-800</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-12700</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-30500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-6100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-6800</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="3">
         <v>13100</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1595,8 +1659,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1636,90 +1703,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>700</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>700</v>
       </c>
       <c r="F32" s="3">
+        <v>700</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>400</v>
       </c>
       <c r="H32" s="3">
         <v>400</v>
       </c>
       <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-53600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1759,95 +1835,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-53600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43921</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43555</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1863,8 +1948,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1880,49 +1966,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>85200</v>
+      </c>
+      <c r="E41" s="3">
         <v>9200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>57400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1962,67 +2052,73 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>5800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>36200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>37000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7800</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2038,96 +2134,105 @@
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>62800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>30100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>47900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>52000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>58500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>97700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>95300</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2140,35 +2245,38 @@
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H47" s="3">
         <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
         <v>1500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>23900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>57800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>81300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>70600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2178,11 +2286,11 @@
       <c r="E48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
@@ -2194,22 +2302,25 @@
         <v>100</v>
       </c>
       <c r="K48" s="3">
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>1300</v>
       </c>
       <c r="O48" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2249,8 +2360,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2290,8 +2404,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2331,8 +2448,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2348,32 +2468,35 @@
       <c r="G52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
         <v>10100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>3800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>33700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2413,49 +2536,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E54" s="3">
         <v>16900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>60200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>80500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>133300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>146800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>173300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2471,8 +2600,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2488,8 +2618,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2529,131 +2660,143 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
         <v>10000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>9700</v>
       </c>
       <c r="F58" s="3">
         <v>9700</v>
       </c>
       <c r="G58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="H58" s="3">
         <v>37200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E60" s="3">
         <v>11500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>50500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2676,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>20000</v>
@@ -2691,27 +2834,30 @@
         <v>20000</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+        <v>20000</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -2720,22 +2866,25 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2775,8 +2924,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2816,8 +2968,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2857,49 +3012,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11700</v>
+        <v>3700</v>
       </c>
       <c r="E66" s="3">
         <v>11700</v>
       </c>
       <c r="F66" s="3">
+        <v>11700</v>
+      </c>
+      <c r="G66" s="3">
         <v>11000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>46800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2915,8 +3076,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2956,8 +3118,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2997,8 +3162,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3038,8 +3206,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3079,49 +3250,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-57900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-54500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-52300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-53100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-45200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-36300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-25000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>52200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>62600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>69800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>62300</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3161,8 +3338,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3202,8 +3382,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3243,49 +3426,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>138400</v>
+      </c>
+      <c r="E76" s="3">
         <v>5200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>100400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>114600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>126500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>120500</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3325,95 +3514,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43921</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43555</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-53600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3429,8 +3627,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3440,11 +3639,11 @@
       <c r="E83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
@@ -3458,8 +3657,8 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3470,8 +3669,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3511,8 +3713,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3552,8 +3757,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3593,8 +3801,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3634,8 +3845,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3675,23 +3889,26 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>5</v>
       </c>
@@ -3704,8 +3921,8 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -3716,8 +3933,11 @@
       <c r="O89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3733,8 +3953,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3774,8 +3995,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3815,8 +4039,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3856,23 +4083,26 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="E94" s="3">
         <v>1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>20000</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3885,8 +4115,8 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -3897,8 +4127,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3914,8 +4147,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3955,8 +4189,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3996,8 +4233,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4037,8 +4277,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4078,23 +4321,26 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>131300</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-27500</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4107,8 +4353,8 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -4119,23 +4365,26 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3100</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4148,8 +4397,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4160,23 +4409,26 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E102" s="3">
         <v>2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11900</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H102" s="3" t="s">
         <v>5</v>
       </c>
@@ -4189,8 +4441,8 @@
       <c r="K102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -4199,6 +4451,9 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>AHG</t>
   </si>
@@ -663,13 +663,10 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -696,22 +693,22 @@
         <v>45382</v>
       </c>
       <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44286</v>
       </c>
       <c r="K7" s="2">
         <v>44104</v>
@@ -737,25 +734,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="E8" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F8" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="G8" s="3">
-        <v>11900</v>
+        <v>400</v>
       </c>
       <c r="H8" s="3">
-        <v>5800</v>
+        <v>700</v>
       </c>
       <c r="I8" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="K8" s="3">
         <v>1400</v>
@@ -781,25 +778,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="E9" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="F9" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="G9" s="3">
-        <v>10700</v>
+        <v>400</v>
       </c>
       <c r="H9" s="3">
+        <v>600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>600</v>
+      </c>
+      <c r="J9" s="3">
         <v>5400</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -825,25 +822,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>400</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="J10" s="3">
+        <v>600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -895,17 +892,17 @@
       <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="3">
-        <v>100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>200</v>
-      </c>
-      <c r="J12" s="3">
-        <v>200</v>
+      <c r="G12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K12" s="3">
         <v>300</v>
@@ -986,14 +983,14 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="3">
-        <v>1600</v>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1078,25 +1075,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7800</v>
+        <v>3900</v>
       </c>
       <c r="E17" s="3">
-        <v>3200</v>
+        <v>3900</v>
       </c>
       <c r="F17" s="3">
-        <v>14500</v>
+        <v>1600</v>
       </c>
       <c r="G17" s="3">
-        <v>12100</v>
+        <v>1600</v>
       </c>
       <c r="H17" s="3">
-        <v>500</v>
+        <v>7700</v>
       </c>
       <c r="I17" s="3">
-        <v>8700</v>
+        <v>7700</v>
       </c>
       <c r="J17" s="3">
-        <v>4200</v>
+        <v>6000</v>
       </c>
       <c r="K17" s="3">
         <v>18000</v>
@@ -1122,25 +1119,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6300</v>
+        <v>-3200</v>
       </c>
       <c r="E18" s="3">
-        <v>-2300</v>
+        <v>-3200</v>
       </c>
       <c r="F18" s="3">
-        <v>-13200</v>
+        <v>-1200</v>
       </c>
       <c r="G18" s="3">
-        <v>-200</v>
+        <v>-1200</v>
       </c>
       <c r="H18" s="3">
-        <v>5300</v>
+        <v>-7000</v>
       </c>
       <c r="I18" s="3">
-        <v>-8500</v>
+        <v>-7000</v>
       </c>
       <c r="J18" s="3">
-        <v>-4200</v>
+        <v>-100</v>
       </c>
       <c r="K18" s="3">
         <v>-16600</v>
@@ -1184,25 +1181,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>400</v>
+      </c>
+      <c r="G20" s="3">
+        <v>400</v>
+      </c>
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-400</v>
-      </c>
       <c r="I20" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>-900</v>
       </c>
       <c r="K20" s="3">
         <v>-800</v>
@@ -1228,25 +1225,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-6100</v>
+        <v>-3000</v>
       </c>
       <c r="E21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
+      <c r="F21" s="3">
+        <v>-1500</v>
       </c>
       <c r="G21" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+        <v>-1500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1271,26 +1268,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1316,25 +1313,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-6100</v>
+        <v>-3000</v>
       </c>
       <c r="E23" s="3">
         <v>-3000</v>
       </c>
       <c r="F23" s="3">
-        <v>-13900</v>
+        <v>-1500</v>
       </c>
       <c r="G23" s="3">
-        <v>1700</v>
+        <v>-1500</v>
       </c>
       <c r="H23" s="3">
-        <v>4900</v>
+        <v>-7400</v>
       </c>
       <c r="I23" s="3">
-        <v>-8900</v>
+        <v>-7400</v>
       </c>
       <c r="J23" s="3">
-        <v>-4300</v>
+        <v>800</v>
       </c>
       <c r="K23" s="3">
         <v>-17400</v>
@@ -1372,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1448,25 +1445,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6100</v>
+        <v>-3000</v>
       </c>
       <c r="E26" s="3">
-        <v>-3100</v>
+        <v>-3000</v>
       </c>
       <c r="F26" s="3">
-        <v>-13900</v>
+        <v>-1500</v>
       </c>
       <c r="G26" s="3">
-        <v>1600</v>
+        <v>-1500</v>
       </c>
       <c r="H26" s="3">
-        <v>4800</v>
+        <v>-7400</v>
       </c>
       <c r="I26" s="3">
-        <v>-8900</v>
+        <v>-7400</v>
       </c>
       <c r="J26" s="3">
-        <v>-4300</v>
+        <v>800</v>
       </c>
       <c r="K26" s="3">
         <v>-17500</v>
@@ -1492,25 +1489,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6000</v>
+        <v>-3000</v>
       </c>
       <c r="E27" s="3">
-        <v>-3100</v>
+        <v>-3000</v>
       </c>
       <c r="F27" s="3">
-        <v>-14000</v>
+        <v>-1700</v>
       </c>
       <c r="G27" s="3">
-        <v>1600</v>
+        <v>-1700</v>
       </c>
       <c r="H27" s="3">
-        <v>4800</v>
+        <v>-1100</v>
       </c>
       <c r="I27" s="3">
-        <v>-8900</v>
+        <v>-1100</v>
       </c>
       <c r="J27" s="3">
-        <v>-4300</v>
+        <v>400</v>
       </c>
       <c r="K27" s="3">
         <v>-17500</v>
@@ -1583,22 +1580,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H29" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I29" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J29" s="3">
         <v>-400</v>
-      </c>
-      <c r="F29" s="3">
-        <v>11800</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-30500</v>
       </c>
       <c r="K29" s="3">
         <v>-6100</v>
@@ -1712,25 +1709,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
-        <v>700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>400</v>
-      </c>
       <c r="I32" s="3">
-        <v>400</v>
+        <v>-300</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="K32" s="3">
         <v>800</v>
@@ -1756,25 +1753,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6000</v>
+        <v>-3000</v>
       </c>
       <c r="E33" s="3">
-        <v>-3500</v>
+        <v>-3000</v>
       </c>
       <c r="F33" s="3">
-        <v>-2200</v>
+        <v>-1700</v>
       </c>
       <c r="G33" s="3">
-        <v>800</v>
+        <v>-1700</v>
       </c>
       <c r="H33" s="3">
-        <v>-7900</v>
+        <v>-1100</v>
       </c>
       <c r="I33" s="3">
-        <v>-8900</v>
+        <v>-1100</v>
       </c>
       <c r="J33" s="3">
-        <v>-34800</v>
+        <v>400</v>
       </c>
       <c r="K33" s="3">
         <v>-23600</v>
@@ -1844,25 +1841,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6000</v>
+        <v>-3000</v>
       </c>
       <c r="E35" s="3">
-        <v>-3500</v>
+        <v>-3000</v>
       </c>
       <c r="F35" s="3">
-        <v>-2200</v>
+        <v>-1700</v>
       </c>
       <c r="G35" s="3">
-        <v>800</v>
+        <v>-1700</v>
       </c>
       <c r="H35" s="3">
-        <v>-7900</v>
+        <v>-1100</v>
       </c>
       <c r="I35" s="3">
-        <v>-8900</v>
+        <v>-1100</v>
       </c>
       <c r="J35" s="3">
-        <v>-34800</v>
+        <v>400</v>
       </c>
       <c r="K35" s="3">
         <v>-23600</v>
@@ -1896,22 +1893,22 @@
         <v>45382</v>
       </c>
       <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44286</v>
       </c>
       <c r="K38" s="2">
         <v>44104</v>
@@ -1976,22 +1973,22 @@
         <v>85200</v>
       </c>
       <c r="E41" s="3">
+        <v>85200</v>
+      </c>
+      <c r="F41" s="3">
         <v>9200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>9200</v>
+      </c>
+      <c r="H41" s="3">
         <v>7900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J41" s="3">
         <v>10000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>18400</v>
-      </c>
-      <c r="I41" s="3">
-        <v>15500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>15100</v>
       </c>
       <c r="K41" s="3">
         <v>21900</v>
@@ -2023,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -2064,22 +2061,22 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>5800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H43" s="3">
         <v>9200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J43" s="3">
         <v>7900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>20000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>6600</v>
-      </c>
-      <c r="J43" s="3">
-        <v>14400</v>
       </c>
       <c r="K43" s="3">
         <v>18300</v>
@@ -2108,22 +2105,22 @@
         <v>200</v>
       </c>
       <c r="E44" s="3">
+        <v>200</v>
+      </c>
+      <c r="F44" s="3">
         <v>1200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H44" s="3">
         <v>1700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J44" s="3">
         <v>900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>7800</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
@@ -2152,22 +2149,22 @@
         <v>56700</v>
       </c>
       <c r="E45" s="3">
-        <v>600</v>
-      </c>
-      <c r="F45" s="3">
+        <v>56700</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J45" s="3">
         <v>2100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>16600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>600</v>
       </c>
       <c r="K45" s="3">
         <v>7700</v>
@@ -2196,22 +2193,22 @@
         <v>142000</v>
       </c>
       <c r="E46" s="3">
+        <v>142000</v>
+      </c>
+      <c r="F46" s="3">
         <v>16900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>16900</v>
+      </c>
+      <c r="H46" s="3">
         <v>20500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>20500</v>
+      </c>
+      <c r="J46" s="3">
         <v>20900</v>
-      </c>
-      <c r="H46" s="3">
-        <v>62800</v>
-      </c>
-      <c r="I46" s="3">
-        <v>22300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>30100</v>
       </c>
       <c r="K46" s="3">
         <v>47900</v>
@@ -2248,14 +2245,14 @@
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>1500</v>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>12200</v>
@@ -2289,17 +2286,17 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>100</v>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -2471,8 +2468,8 @@
       <c r="H52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I52" s="3">
-        <v>10100</v>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -2548,22 +2545,22 @@
         <v>142000</v>
       </c>
       <c r="E54" s="3">
+        <v>142000</v>
+      </c>
+      <c r="F54" s="3">
         <v>16900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>16900</v>
+      </c>
+      <c r="H54" s="3">
         <v>20500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>20500</v>
+      </c>
+      <c r="J54" s="3">
         <v>20900</v>
-      </c>
-      <c r="H54" s="3">
-        <v>62800</v>
-      </c>
-      <c r="I54" s="3">
-        <v>32500</v>
-      </c>
-      <c r="J54" s="3">
-        <v>31700</v>
       </c>
       <c r="K54" s="3">
         <v>60200</v>
@@ -2624,26 +2621,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2672,22 +2669,22 @@
         <v>2000</v>
       </c>
       <c r="E58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F58" s="3">
         <v>10000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H58" s="3">
         <v>9700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>9700</v>
       </c>
-      <c r="H58" s="3">
-        <v>37200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>12000</v>
-      </c>
       <c r="J58" s="3">
-        <v>13000</v>
+        <v>9700</v>
       </c>
       <c r="K58" s="3">
         <v>2700</v>
@@ -2713,25 +2710,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="H59" s="3">
-        <v>13400</v>
+        <v>1000</v>
       </c>
       <c r="I59" s="3">
         <v>1000</v>
       </c>
       <c r="J59" s="3">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="K59" s="3">
         <v>10400</v>
@@ -2760,22 +2757,22 @@
         <v>3600</v>
       </c>
       <c r="E60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F60" s="3">
         <v>11500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H60" s="3">
         <v>11600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J60" s="3">
         <v>11000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>50500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>13000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>14400</v>
       </c>
       <c r="K60" s="3">
         <v>13100</v>
@@ -2844,26 +2841,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3021,25 +3018,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="E66" s="3">
-        <v>11700</v>
+        <v>3600</v>
       </c>
       <c r="F66" s="3">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="G66" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>11600</v>
+      </c>
+      <c r="I66" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J66" s="3">
         <v>11000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>50500</v>
-      </c>
-      <c r="I66" s="3">
-        <v>13000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>14400</v>
       </c>
       <c r="K66" s="3">
         <v>33100</v>
@@ -3262,22 +3259,22 @@
         <v>-63900</v>
       </c>
       <c r="E72" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-57900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="H72" s="3">
         <v>-54500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="J72" s="3">
         <v>-52300</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-53100</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-45200</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-36300</v>
       </c>
       <c r="K72" s="3">
         <v>-25000</v>
@@ -3438,22 +3435,22 @@
         <v>138400</v>
       </c>
       <c r="E76" s="3">
+        <v>138400</v>
+      </c>
+      <c r="F76" s="3">
         <v>5200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H76" s="3">
         <v>8700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J76" s="3">
         <v>9900</v>
-      </c>
-      <c r="H76" s="3">
-        <v>12300</v>
-      </c>
-      <c r="I76" s="3">
-        <v>19600</v>
-      </c>
-      <c r="J76" s="3">
-        <v>17300</v>
       </c>
       <c r="K76" s="3">
         <v>27100</v>
@@ -3531,22 +3528,22 @@
         <v>45382</v>
       </c>
       <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44286</v>
       </c>
       <c r="K80" s="2">
         <v>44104</v>
@@ -3572,25 +3569,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6000</v>
+        <v>-3000</v>
       </c>
       <c r="E81" s="3">
-        <v>-3500</v>
+        <v>-3000</v>
       </c>
       <c r="F81" s="3">
-        <v>-2200</v>
+        <v>-1700</v>
       </c>
       <c r="G81" s="3">
-        <v>800</v>
+        <v>-1700</v>
       </c>
       <c r="H81" s="3">
-        <v>-7900</v>
+        <v>-1100</v>
       </c>
       <c r="I81" s="3">
-        <v>-8900</v>
+        <v>-1100</v>
       </c>
       <c r="J81" s="3">
-        <v>-34800</v>
+        <v>400</v>
       </c>
       <c r="K81" s="3">
         <v>-23600</v>
@@ -3642,8 +3639,8 @@
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
@@ -3651,8 +3648,8 @@
       <c r="I83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -3898,25 +3895,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="E89" s="3">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F89" s="3">
-        <v>-1900</v>
+        <v>100</v>
       </c>
       <c r="G89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-700</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
@@ -3959,26 +3956,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4092,25 +4089,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-56300</v>
+        <v>-28100</v>
       </c>
       <c r="E94" s="3">
-        <v>1500</v>
+        <v>-28100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1500</v>
+        <v>800</v>
       </c>
       <c r="G94" s="3">
-        <v>20000</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
+        <v>800</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>10000</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -4153,26 +4150,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4330,25 +4327,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>131300</v>
+        <v>65700</v>
       </c>
       <c r="E100" s="3">
-        <v>400</v>
+        <v>65700</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G100" s="3">
-        <v>-27500</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-13800</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -4374,16 +4371,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
-        <v>200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>2700</v>
-      </c>
       <c r="G101" s="3">
-        <v>-3100</v>
+        <v>-1500</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>5</v>
@@ -4391,8 +4388,8 @@
       <c r="I101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
+      <c r="J101" s="3">
+        <v>100</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -4418,25 +4415,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>74700</v>
+        <v>37400</v>
       </c>
       <c r="E102" s="3">
-        <v>2300</v>
+        <v>37400</v>
       </c>
       <c r="F102" s="3">
-        <v>-800</v>
+        <v>1200</v>
       </c>
       <c r="G102" s="3">
-        <v>-11900</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
+        <v>1200</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-6000</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
   <si>
     <t>AHG</t>
   </si>
@@ -656,154 +656,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43921</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43555</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F9" s="3">
         <v>700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>5400</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -816,16 +830,22 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -834,20 +854,20 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -860,8 +880,14 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +904,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,26 +932,32 @@
       <c r="J12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +1000,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -995,23 +1035,29 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>29200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1100,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1121,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F17" s="3">
         <v>3900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>7700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>18000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>49300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>14800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>12600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>10900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-7000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-7000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-16600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-47500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-10300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-7700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-7200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,82 +1241,90 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>900</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>400</v>
       </c>
       <c r="P20" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>400</v>
+      </c>
+      <c r="R20" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-7400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1263,8 +1337,14 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1289,11 +1369,11 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1307,52 +1387,64 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-17400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-47500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-9400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-6800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1378,25 +1470,31 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1537,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-17500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-46900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-10400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-7600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-17500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-46900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-10400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-7200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-7600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1687,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1583,40 +1705,46 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>-200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>6300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>6300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-6100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-6800</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3">
         <v>13100</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1787,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1837,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-900</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-400</v>
       </c>
       <c r="P32" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-23600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-53600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-10400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-7200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>5500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1987,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-23600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-53600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-10400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-7200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>5500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43921</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43555</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2116,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2136,60 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>91400</v>
+      </c>
+      <c r="F41" s="3">
         <v>85200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>85200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>14900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>25900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>57400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2020,17 +2200,17 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2052,52 +2232,64 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>5800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>9200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>9200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>7900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>18300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>36200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>19800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>29800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>37000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2108,128 +2300,146 @@
         <v>200</v>
       </c>
       <c r="F44" s="3">
+        <v>200</v>
+      </c>
+      <c r="G44" s="3">
+        <v>200</v>
+      </c>
+      <c r="H44" s="3">
         <v>1200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F45" s="3">
         <v>56700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>56700</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>7700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>9100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>3100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>100200</v>
+      </c>
+      <c r="F46" s="3">
         <v>142000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>142000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>16900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>16900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>20500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>20500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>20900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>47900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>52000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>37900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>58500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>97700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>95300</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2254,34 +2464,40 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>12200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>23900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>57800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>81300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>70600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>200</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>5</v>
@@ -2295,37 +2511,43 @@
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>112500</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>112500</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2360,8 +2582,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2632,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2682,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2474,26 +2714,32 @@
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>3800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>33700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2782,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>212900</v>
+      </c>
+      <c r="F54" s="3">
         <v>142000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>142000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>16900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>16900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>20500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>20900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>60200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>80500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>133300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>146800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>173300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2856,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,16 +2876,18 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>5</v>
@@ -2642,11 +2904,11 @@
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2660,60 +2922,72 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>10000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>10000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>9700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>9700</v>
       </c>
       <c r="J58" s="3">
         <v>9700</v>
       </c>
       <c r="K58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="L58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="M58" s="3">
         <v>2700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="E59" s="3">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="F59" s="3">
         <v>500</v>
@@ -2722,86 +2996,98 @@
         <v>500</v>
       </c>
       <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>500</v>
+      </c>
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>10400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>16700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>11500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>26600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>11500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>11500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>13100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>12400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>12000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>11500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>26600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2819,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>20000</v>
@@ -2834,10 +3120,16 @@
         <v>20000</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+        <v>20000</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2862,26 +3154,32 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3222,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3272,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3322,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>33100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>32400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>32900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>32200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>46800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3396,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3442,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3492,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3542,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3592,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-64500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-64500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-63900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-63900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-57900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-57900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-54500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-54500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-52300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-25000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>52200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>62600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>69800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>62300</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3692,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3742,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3792,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>200600</v>
+      </c>
+      <c r="F76" s="3">
         <v>138400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>138400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>27100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>48100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>100400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>114600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>126500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>120500</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3892,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43921</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43555</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-23600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-53600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-10400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-7200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>5500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +4021,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3648,20 +4046,20 @@
       <c r="I83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -3669,8 +4067,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4117,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4167,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4217,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4267,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,43 +4317,49 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
@@ -3933,8 +4367,14 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,16 +4391,18 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>5</v>
@@ -3977,11 +4419,11 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3995,8 +4437,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4487,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,43 +4537,49 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-28100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-28100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>10000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -4127,8 +4587,14 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4611,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,11 +4639,11 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4189,8 +4657,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4707,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4757,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,43 +4807,49 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>33600</v>
+      </c>
+      <c r="F100" s="3">
         <v>65700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>65700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-13800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -4365,43 +4857,49 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4409,48 +4907,60 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F102" s="3">
         <v>37400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>37400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>AHG</t>
   </si>
@@ -656,174 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F8" s="3">
         <v>3500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F9" s="3">
         <v>3400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>5400</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
@@ -836,23 +849,29 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
@@ -860,20 +879,20 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
@@ -886,8 +905,14 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +931,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,26 +965,32 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1900</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,16 +1039,22 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>81200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -1041,31 +1080,37 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>29200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1106,8 +1151,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1174,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F17" s="3">
         <v>3700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>18000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>49300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>14800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>12600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>10900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-7000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-16600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-47500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-10300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-7200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,8 +1308,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1255,82 +1322,88 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>400</v>
       </c>
       <c r="R20" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>400</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-7400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1343,8 +1416,14 @@
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1375,11 +1454,11 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1393,66 +1472,78 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-82900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-82900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-7400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-17400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-47500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-9400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-6800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-15400</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-15400</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1476,25 +1567,31 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1640,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-17500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-46900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-10400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-17500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-46900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-10400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1808,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1711,40 +1832,46 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>6300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>6300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-6100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-6800</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
         <v>13100</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1920,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,8 +1976,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1855,96 +1994,108 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-400</v>
       </c>
       <c r="R32" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-23600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-53600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-10400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>5500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2144,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-23600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-53600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-10400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>5500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2287,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,58 +2309,66 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>176200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>176200</v>
+      </c>
+      <c r="F41" s="3">
         <v>91400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>91400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>85200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>85200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>21900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>14900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>25900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>57400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2206,17 +2385,17 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>100</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2238,58 +2417,70 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>5800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>9200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>9200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>7900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>18300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>36200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>19800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>29800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>37000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2306,140 +2497,158 @@
         <v>200</v>
       </c>
       <c r="H44" s="3">
+        <v>200</v>
+      </c>
+      <c r="I44" s="3">
+        <v>200</v>
+      </c>
+      <c r="J44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>900</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F45" s="3">
         <v>8200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>8200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>56700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>56700</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>7700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>9100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>196100</v>
+      </c>
+      <c r="F46" s="3">
         <v>100200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>100200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>142000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>142000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>16900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>16900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>20500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>20500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>20900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>47900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>52000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>37900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>58500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>97700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>95300</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2470,41 +2679,47 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3">
         <v>12200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>23900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>57800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>81300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>70600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2517,44 +2732,50 @@
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F49" s="3">
         <v>112500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>112500</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -2588,8 +2809,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2865,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2921,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2720,26 +2959,32 @@
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>3800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>33700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +3033,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F54" s="3">
         <v>212900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>212900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>142000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>142000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>16900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>20500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>20500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>20900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>60200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>80500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>133300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>146800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>173300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +3115,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,23 +3137,25 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2910,11 +3171,11 @@
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -2928,72 +3189,84 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F58" s="3">
         <v>4700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>10000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>10000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>9700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>9700</v>
       </c>
       <c r="L58" s="3">
         <v>9700</v>
       </c>
       <c r="M58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O58" s="3">
         <v>2700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F59" s="3">
         <v>6000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>500</v>
       </c>
       <c r="H59" s="3">
         <v>500</v>
@@ -3002,99 +3275,111 @@
         <v>500</v>
       </c>
       <c r="J59" s="3">
+        <v>500</v>
+      </c>
+      <c r="K59" s="3">
+        <v>500</v>
+      </c>
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>10400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>16700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>11300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>11500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>26600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F60" s="3">
         <v>12200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>12200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>11600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>11000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>12400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>12000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>26600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -3111,10 +3396,10 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>20000</v>
@@ -3126,10 +3411,16 @@
         <v>20000</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+        <v>20000</v>
+      </c>
+      <c r="S61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3160,26 +3451,32 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3525,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3581,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3637,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F66" s="3">
         <v>12300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>11600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>11000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>33100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>32400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>32900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>32200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>46800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3719,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3771,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3827,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3883,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3939,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-198900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-198900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-64500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-64500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-63900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-63900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-57900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-57900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-54500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-54500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-52300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-25000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>52200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>62600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>69800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>62300</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +4051,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +4107,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +4163,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>199100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>199100</v>
+      </c>
+      <c r="F76" s="3">
         <v>200600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>200600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>138400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>138400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>27100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>48100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>100400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>114600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>126500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>120500</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4275,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-23600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-53600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-10400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>5500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4418,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4052,20 +4449,20 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4073,8 +4470,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4526,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4582,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4638,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4694,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,49 +4750,55 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -4373,8 +4806,14 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,23 +4832,25 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>5</v>
       </c>
@@ -4425,11 +4866,11 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -4443,8 +4884,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4940,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,49 +4996,55 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-28200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-28200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-28100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-28100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>10000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -4593,8 +5052,14 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +5078,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4645,11 +5112,11 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -4663,8 +5130,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +5186,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5242,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,49 +5298,55 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>64300</v>
+      </c>
+      <c r="F100" s="3">
         <v>33600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>33600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>65700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>65700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-13800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -4863,49 +5354,55 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -4913,54 +5410,66 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>41900</v>
+      </c>
+      <c r="F102" s="3">
         <v>3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>37400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>37400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>AHG</t>
   </si>
@@ -656,193 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F8" s="3">
         <v>3900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F9" s="3">
         <v>4200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>5400</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -855,29 +869,35 @@
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>-200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
@@ -885,20 +905,20 @@
         <v>0</v>
       </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -911,8 +931,14 @@
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +959,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,26 +999,32 @@
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>2200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1900</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,23 +1079,29 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>81200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>81200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1086,38 +1126,44 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>29200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>600</v>
+      </c>
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1157,8 +1203,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1228,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F17" s="3">
         <v>5600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>18000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>49300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>14800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>12600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>10900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-7000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-7000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-16600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-10300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-7700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-7200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,8 +1376,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1328,88 +1396,94 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>400</v>
       </c>
       <c r="T20" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>400</v>
+      </c>
+      <c r="V20" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-7400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-7400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1422,8 +1496,14 @@
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1460,11 +1540,11 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1478,79 +1558,91 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-82900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-82900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-7400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-17400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-9400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-6600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-6800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-15400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-15400</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1573,25 +1665,31 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1744,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-67500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-67500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-17500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-10400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-7200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-7600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-67200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-67200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-17500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-46900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-10400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-7200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-7600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1930,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1838,40 +1960,46 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>6300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>6300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-6100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
         <v>13100</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2054,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,8 +2116,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2000,102 +2140,114 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-400</v>
       </c>
       <c r="T32" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-67200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-67200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-23600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-10400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-7200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>5500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2302,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-67200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-67200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-23600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-10400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-7200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>5500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2459,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2483,72 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F41" s="3">
         <v>176200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>176200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>91400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>91400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>85200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>85200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>21900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>25900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>57400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2391,17 +2571,17 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2423,64 +2603,76 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F43" s="3">
         <v>12900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>12900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>5800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>9200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>9200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>18300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>36200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>19800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>29800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>37000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2503,152 +2695,170 @@
         <v>200</v>
       </c>
       <c r="J44" s="3">
+        <v>200</v>
+      </c>
+      <c r="K44" s="3">
+        <v>200</v>
+      </c>
+      <c r="L44" s="3">
         <v>1200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>900</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F45" s="3">
         <v>6800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>8200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>8200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>56700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>56700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>7700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>9100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>3300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F46" s="3">
         <v>196100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>196100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>100200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>100200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>142000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>142000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>16900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>20500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>20500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>20900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>47900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>52000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>37900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>58500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>97700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>95300</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2685,26 +2895,32 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3">
         <v>12200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>23900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>57800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>81300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>70600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2715,17 +2931,17 @@
         <v>100</v>
       </c>
       <c r="F48" s="3">
+        <v>100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>100</v>
+      </c>
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2738,50 +2954,56 @@
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>17900</v>
+      </c>
+      <c r="F49" s="3">
         <v>18700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>18700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>112500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>112500</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -2815,8 +3037,14 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3099,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,16 +3161,22 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3">
+        <v>175700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>175700</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
@@ -2965,26 +3205,32 @@
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>3800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>33700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3285,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>212000</v>
+      </c>
+      <c r="F54" s="3">
         <v>215000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>215000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>212900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>212900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>142000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>142000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>16900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>16900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>20500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>20500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>20900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>60200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>80500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>133300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>146800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>173300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3375,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,8 +3399,10 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3150,18 +3412,18 @@
       <c r="E57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3177,11 +3439,11 @@
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -3195,8 +3457,14 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3207,72 +3475,78 @@
         <v>2000</v>
       </c>
       <c r="F58" s="3">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="G58" s="3">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I58" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J58" s="3">
         <v>2000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>10000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>10000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>9700</v>
       </c>
       <c r="N58" s="3">
         <v>9700</v>
       </c>
       <c r="O58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="P58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F59" s="3">
         <v>10300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>10300</v>
       </c>
-      <c r="F59" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>6000</v>
-      </c>
       <c r="H59" s="3">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="I59" s="3">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="J59" s="3">
         <v>500</v>
@@ -3281,90 +3555,102 @@
         <v>500</v>
       </c>
       <c r="L59" s="3">
+        <v>500</v>
+      </c>
+      <c r="M59" s="3">
+        <v>500</v>
+      </c>
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>10400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>16700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>11300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>11500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>26600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F60" s="3">
         <v>13800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>13800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>12200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>12200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>11500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>11600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>11600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>11000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>13100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>12400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>12000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>11500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>26600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3375,17 +3661,17 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -3402,10 +3688,10 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>20000</v>
@@ -3417,10 +3703,16 @@
         <v>20000</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+        <v>20000</v>
+      </c>
+      <c r="U61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3457,26 +3749,32 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3829,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3891,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3953,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F66" s="3">
         <v>15800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>15800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>11500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>11600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>11600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>11000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>33100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>32400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>32900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>32200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>46800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4043,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4101,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +4163,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4225,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4287,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-200200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-200200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-198900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-198900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-64500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-64500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-63900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-63900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-57900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-57900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-54500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-54500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-52300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-25000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>52200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>62600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>69800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>62300</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4411,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4473,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4535,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>198300</v>
+      </c>
+      <c r="F76" s="3">
         <v>199100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>199100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>200600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>200600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>138400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>138400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>27100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>48100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>100400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>114600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>126500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>120500</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4659,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-67200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-67200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-23600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-10400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-7200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>5500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,16 +4816,18 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
@@ -4455,20 +4853,20 @@
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4476,8 +4874,14 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4936,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4998,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5060,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5122,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,55 +5184,61 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>600</v>
+      </c>
+      <c r="F89" s="3">
         <v>3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
@@ -4812,8 +5246,14 @@
       <c r="T89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,29 +5274,31 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-87800</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-87800</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
@@ -4872,11 +5314,11 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4890,8 +5332,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5394,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,55 +5456,61 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-24800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-24800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-28200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-28200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-28100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-28100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>10000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -5058,8 +5518,14 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5546,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5118,11 +5586,11 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5136,8 +5604,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5666,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5728,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,55 +5790,61 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>64300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>64300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>33600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>33600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>65700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>65700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-13800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -5360,55 +5852,61 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -5416,60 +5914,72 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-82600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-82600</v>
+      </c>
+      <c r="F102" s="3">
         <v>41900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>41900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>37400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>37400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>
